--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2018_aysen.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2018_aysen.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:39</t>
+    <t xml:space="preserve">2026-10-05 01:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>917346.62</v>
+        <v>917346.63</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>926506.25</v>
@@ -604,7 +604,7 @@
         <v>1145019.88</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
@@ -623,7 +623,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1221386.62</v>
+        <v>1221386.63</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>1240862.75</v>
